--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sat May 09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -999,6 +999,11 @@
           <t>viviendagob</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>viviendagob.bsky.social</t>
@@ -1043,7 +1048,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1075,7 +1080,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1117,7 +1122,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1127,7 +1132,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>Tue Jan 21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1169,7 +1174,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1238,7 +1243,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1275,7 +1280,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1285,7 +1290,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1317,7 +1322,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1359,7 +1364,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1369,7 +1374,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1401,7 +1406,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu Jan 28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1433,7 +1438,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1443,7 +1448,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1475,7 +1480,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1485,7 +1490,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1517,7 +1522,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1527,7 +1532,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1591,7 +1596,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1623,7 +1628,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1633,7 +1638,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1665,7 +1670,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1697,7 +1702,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1729,7 +1734,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1761,7 +1766,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1793,7 +1798,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1835,7 +1840,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1867,7 +1872,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1904,7 +1909,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1936,12 +1941,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>lyadelestado</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1973,7 +1983,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2010,7 +2020,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2020,7 +2030,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2052,7 +2062,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2084,7 +2094,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2094,7 +2104,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2126,7 +2136,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2158,7 +2168,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2190,7 +2200,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>Tue Jan 21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2200,7 +2210,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2235,6 +2245,11 @@
           <t>saraaagesen.bsky.social</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>prensa@miteco.gob.es</t>
@@ -2264,7 +2279,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2274,7 +2289,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2306,7 +2321,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2316,7 +2331,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2348,7 +2363,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu Nov 24</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2407,7 +2422,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2449,7 +2464,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2459,7 +2474,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2491,7 +2506,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2523,7 +2538,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2555,7 +2570,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2597,7 +2612,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2639,7 +2654,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>Mon Jan 20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2649,7 +2664,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2681,7 +2696,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2691,7 +2706,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2723,7 +2738,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2733,7 +2748,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2765,7 +2780,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>Mon Jan 20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2775,7 +2790,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2807,7 +2822,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2839,7 +2854,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2871,7 +2886,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2881,7 +2896,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2913,7 +2928,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2955,7 +2970,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2987,7 +3002,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3014,7 +3029,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3024,7 +3039,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3083,7 +3098,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3135,7 +3150,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3177,7 +3192,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3229,7 +3244,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3311,6 +3326,11 @@
           <t>RoAguirreGil</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>Diputado/a</t>
@@ -3345,7 +3365,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3387,7 +3407,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3429,7 +3449,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3439,7 +3459,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3481,7 +3501,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3518,7 +3538,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3570,7 +3590,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3612,7 +3632,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3657,6 +3677,11 @@
           <t>EmiliaAlmo13648</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wed Dec 06</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>emilia.almodovar@congreso.es</t>
@@ -3696,7 +3721,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3706,7 +3731,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3746,6 +3771,11 @@
           <t>pilaraliaa</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>pilar.alia@congreso.es</t>
@@ -3785,7 +3815,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3827,7 +3857,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3869,7 +3899,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3909,6 +3939,11 @@
           <t>pabloantunano78</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Mon Dec 09</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>pabloantunano.bsky.social</t>
@@ -3990,7 +4025,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4042,7 +4077,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4084,7 +4119,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4126,7 +4161,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4168,7 +4203,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4178,7 +4213,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4215,7 +4250,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>Tue Mar 10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4262,7 +4297,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4302,6 +4337,11 @@
           <t>Evarist_Aznar</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sat Jul 13</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Diputado/a</t>
@@ -4334,6 +4374,11 @@
           <t>AzorinLazaro</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed Nov 11</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>lazaro.azorin@congreso.es</t>
@@ -4373,7 +4418,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Sat May 09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4425,7 +4470,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4465,6 +4510,11 @@
           <t>juan_bayon12</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>juan.bayon@congreso.es</t>
@@ -4504,7 +4554,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4546,7 +4596,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4556,7 +4606,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4598,7 +4648,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4640,7 +4690,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4682,7 +4732,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4754,6 +4804,11 @@
           <t>arruegab</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
           <t>gabriel.arrue@congreso.es</t>
@@ -4793,7 +4848,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4835,7 +4890,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4887,7 +4942,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4897,7 +4952,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -4934,7 +4989,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4976,7 +5031,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5018,7 +5073,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5087,7 +5142,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5139,7 +5194,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5191,7 +5246,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5243,7 +5298,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5285,7 +5340,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5327,7 +5382,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5369,7 +5424,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5411,7 +5466,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5453,7 +5508,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5495,7 +5550,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5537,7 +5592,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5579,7 +5634,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>Sat Mar 16</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5621,7 +5676,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5663,7 +5718,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5705,7 +5760,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>Sun May 03</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5747,7 +5802,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5789,7 +5844,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5831,7 +5886,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5905,7 +5960,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>Mon Mar 23</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5915,7 +5970,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -5957,7 +6012,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>Mon Jul 31</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6029,6 +6084,11 @@
           <t>ignasiconesa50</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tue Apr 21</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>iconesa@congreso.es</t>
@@ -6068,7 +6128,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6110,7 +6170,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6162,7 +6222,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6204,7 +6264,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6256,7 +6316,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6308,7 +6368,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6350,7 +6410,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6424,7 +6484,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6466,7 +6526,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -6503,7 +6563,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6545,7 +6605,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6597,7 +6657,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6639,7 +6699,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6681,7 +6741,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -6718,7 +6778,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Sat May 02</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6760,7 +6820,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6802,7 +6862,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6852,6 +6912,11 @@
           <t>rauldiaz_</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>raul.diazmarin@congreso.es</t>
@@ -6889,6 +6954,11 @@
           <t>Yolanda_Diaz_</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tue Jan 21</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>yolandadiaz.bsky.social</t>
@@ -6896,7 +6966,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6938,7 +7008,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -6980,7 +7050,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7022,7 +7092,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7074,7 +7144,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7116,7 +7186,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Thu Apr 23</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7158,7 +7228,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7200,7 +7270,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7242,7 +7312,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -7279,7 +7349,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2019-04-22</t>
+          <t>Mon Apr 22</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7321,7 +7391,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7361,6 +7431,11 @@
           <t>c_fIoriano</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Tue Jul 09</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
           <t>carlos.floriano@congreso.es</t>
@@ -7432,7 +7507,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7474,7 +7549,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -7516,7 +7591,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -7553,7 +7628,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7595,7 +7670,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7642,7 +7717,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7684,7 +7759,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -7724,6 +7799,11 @@
           <t>MgarciaFelix</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Thu Sep 09</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>manuel.garciafelix@congreso.es</t>
@@ -7763,7 +7843,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7852,7 +7932,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7904,7 +7984,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7946,7 +8026,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7988,7 +8068,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8040,7 +8120,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8082,7 +8162,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8156,7 +8236,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -8166,7 +8246,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8208,7 +8288,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Mon Apr 20</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8248,6 +8328,11 @@
           <t>annaherdaro</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Fri Jul 14</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr">
         <is>
           <t>gonzalez.herdaro@congreso.es</t>
@@ -8287,7 +8372,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8297,7 +8382,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8339,7 +8424,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8381,7 +8466,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -8418,7 +8503,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8470,7 +8555,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -8520,6 +8605,11 @@
           <t>miriamguard</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>mirian.guardiola@congreso.es</t>
@@ -8559,7 +8649,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>Wed Aug 09</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8601,7 +8691,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8653,7 +8743,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -8705,7 +8795,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8794,7 +8884,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -8836,7 +8926,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -8878,7 +8968,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8930,7 +9020,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -8972,7 +9062,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -9014,7 +9104,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -9066,7 +9156,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9108,7 +9198,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>Sat May 09</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -9187,7 +9277,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -9281,7 +9371,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 04</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9333,7 +9423,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -9375,7 +9465,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9415,6 +9505,11 @@
           <t>teresajorda</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>teresajorda.bsky.social</t>
@@ -9457,6 +9552,11 @@
           <t>IreneJodar</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
           <t>irene.jodar@congreso.es</t>
@@ -9496,7 +9596,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>Sat May 09</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -9548,7 +9648,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -9590,7 +9690,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>Sat Apr 12</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -9632,7 +9732,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 06</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -9674,7 +9774,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9716,7 +9816,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -9758,7 +9858,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -9795,7 +9895,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -9847,7 +9947,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9889,7 +9989,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9931,7 +10031,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>Sun Apr 12</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9973,7 +10073,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -10025,7 +10125,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -10067,7 +10167,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -10077,7 +10177,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -10119,7 +10219,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -10161,7 +10261,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -10203,7 +10303,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10245,7 +10345,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -10297,7 +10397,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10339,7 +10439,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -10381,7 +10481,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -10423,7 +10523,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -10465,7 +10565,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -10539,7 +10639,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10549,7 +10649,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10591,7 +10691,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -10633,7 +10733,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -10643,7 +10743,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10690,7 +10790,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10730,6 +10830,11 @@
           <t>Antonio3732405</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr">
         <is>
           <t>antonio.martinez@congreso.es</t>
@@ -10769,7 +10874,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>Tue Oct 15</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -10821,7 +10926,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -10863,7 +10968,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -10873,7 +10978,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -10915,7 +11020,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -10957,17 +11062,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>luzseijo.bsky.social</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>luzseijo.bsky.social</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -11009,7 +11114,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -11051,7 +11156,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11061,7 +11166,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -11135,7 +11240,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -11177,7 +11282,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11251,7 +11356,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11293,7 +11398,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>Wed Apr 08</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -11345,7 +11450,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11419,7 +11524,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -11503,7 +11608,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>Wed May 06</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -11545,7 +11650,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -11587,7 +11692,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -11661,7 +11766,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -11698,7 +11803,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>Sat Oct 11</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -11740,7 +11845,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>Mon May 19</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -11814,7 +11919,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11856,7 +11961,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -11898,7 +12003,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -11940,7 +12045,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -11977,7 +12082,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -12029,7 +12134,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12069,6 +12174,11 @@
           <t>cristinanarbona</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>cristinanarbona.bsky.social</t>
@@ -12118,7 +12228,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -12170,7 +12280,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12212,7 +12322,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12296,7 +12406,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -12343,7 +12453,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -12417,7 +12527,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -12469,7 +12579,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -12511,7 +12621,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -12553,7 +12663,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12640,6 +12750,11 @@
           <t>PatriOteroR</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Mon Apr 03</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t>patricia.otero@congreso.es</t>
@@ -12679,7 +12794,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12731,7 +12846,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -12773,7 +12888,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>Sat May 02</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -12815,7 +12930,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -12852,7 +12967,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -12894,7 +13009,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -12936,7 +13051,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -12973,7 +13088,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13015,7 +13130,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -13025,7 +13140,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13067,7 +13182,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -13104,7 +13219,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13146,7 +13261,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -13198,7 +13313,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -13240,7 +13355,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>Wed Apr 24</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -13282,7 +13397,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -13324,7 +13439,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -13366,7 +13481,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -13440,7 +13555,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue Apr 21</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -13480,6 +13595,11 @@
           <t>alvaroperezlop2</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Sat Jun 21</t>
+        </is>
+      </c>
       <c r="I312" t="inlineStr">
         <is>
           <t>alvaro.perez@congreso.es</t>
@@ -13519,7 +13639,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -13571,7 +13691,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -13613,7 +13733,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -13729,7 +13849,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -13771,7 +13891,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Fri May 01</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -13850,7 +13970,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -13902,7 +14022,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -13954,7 +14074,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13996,7 +14116,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -14038,7 +14158,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -14090,7 +14210,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -14142,7 +14262,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -14184,7 +14304,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -14263,7 +14383,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -14305,7 +14425,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -14347,7 +14467,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -14389,7 +14509,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -14399,7 +14519,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -14441,7 +14561,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -14520,7 +14640,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -14530,7 +14650,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14572,7 +14692,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -14614,7 +14734,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -14666,7 +14786,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -14708,7 +14828,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -14750,7 +14870,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -14802,7 +14922,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -14886,7 +15006,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -14928,7 +15048,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -14970,7 +15090,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>Sun Jul 23</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -15012,7 +15132,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -15054,7 +15174,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>Wed Mar 18</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -15096,7 +15216,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -15148,7 +15268,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -15185,7 +15305,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -15222,7 +15342,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 06</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -15264,7 +15384,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -15306,7 +15426,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -15353,7 +15473,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -15447,7 +15567,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -15499,7 +15619,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -15541,7 +15661,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>Thu Nov 21</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -15583,7 +15703,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -15625,7 +15745,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -15677,7 +15797,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
+          <t>Mon Nov 14</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -15719,7 +15839,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -15771,7 +15891,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -15811,6 +15931,11 @@
           <t>EnriqueSantiago</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>enriquesantiago.bsky.social</t>
@@ -15818,7 +15943,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -15892,7 +16017,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -15944,7 +16069,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -15986,7 +16111,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -16028,7 +16153,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -16070,7 +16195,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -16110,6 +16235,11 @@
           <t>dvserrada</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I372" t="inlineStr">
         <is>
           <t>david.serrada@congreso.es</t>
@@ -16149,7 +16279,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -16201,7 +16331,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -16253,7 +16383,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -16337,7 +16467,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -16389,7 +16519,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -16399,7 +16529,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -16441,7 +16571,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -16483,7 +16613,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>Thu Apr 23</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -16525,7 +16655,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -16594,7 +16724,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -16636,7 +16766,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -16678,7 +16808,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -16720,7 +16850,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -16799,7 +16929,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -16841,7 +16971,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -16851,7 +16981,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -16893,7 +17023,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -16935,7 +17065,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -16977,7 +17107,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -17017,6 +17147,11 @@
           <t>CristinaTenienS</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Fri May 08</t>
+        </is>
+      </c>
       <c r="I393" t="inlineStr">
         <is>
           <t>cristina.teniente@congreso.es</t>
@@ -17056,7 +17191,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -17098,7 +17233,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -17140,7 +17275,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -17192,7 +17327,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -17234,7 +17369,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -17276,7 +17411,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -17323,7 +17458,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>Tue Apr 14</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -17439,7 +17574,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -17481,7 +17616,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -17523,7 +17658,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -17565,7 +17700,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -17607,7 +17742,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -17649,7 +17784,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -17723,7 +17858,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -17775,7 +17910,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -17785,7 +17920,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17827,7 +17962,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -17869,7 +18004,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -17911,7 +18046,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -17963,7 +18098,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -18005,7 +18140,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -18047,7 +18182,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -18089,7 +18224,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -18131,7 +18266,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -18156,6 +18291,11 @@
           <t>HakimAbdeselam</t>
         </is>
       </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Mon Apr 06</t>
+        </is>
+      </c>
       <c r="I420" t="inlineStr">
         <is>
           <t>abdelhakim.abdeselam@senado.es</t>
@@ -18215,6 +18355,11 @@
           <t>NereaAhedoCeza</t>
         </is>
       </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K422" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -18244,7 +18389,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Tue Jul 02</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -18291,7 +18436,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -18348,6 +18493,11 @@
           <t>jramoresAlcalde</t>
         </is>
       </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I426" t="inlineStr">
         <is>
           <t>jramon.amores@senado.es</t>
@@ -18382,7 +18532,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -18417,9 +18567,19 @@
           <t>javieranton</t>
         </is>
       </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>javieranton.bsky.social</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -18454,6 +18614,11 @@
           <t>MariolaAranda</t>
         </is>
       </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I429" t="inlineStr">
         <is>
           <t>mariola.aranda@senado.es</t>
@@ -18488,7 +18653,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -18525,7 +18690,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -18582,6 +18747,11 @@
           <t>JAArmijo_Nerja</t>
         </is>
       </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="I433" t="inlineStr">
         <is>
           <t>jalberto.armijo@senado.es</t>
@@ -18616,17 +18786,17 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>martaarocha.bsky.social</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>martaarocha.bsky.social</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -18663,7 +18833,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -18722,7 +18892,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -18759,7 +18929,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -18796,7 +18966,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -18860,7 +19030,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18897,7 +19067,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -18932,6 +19102,11 @@
           <t>uxuebarkos</t>
         </is>
       </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Sat Oct 04</t>
+        </is>
+      </c>
       <c r="I443" t="inlineStr">
         <is>
           <t>uxue.barkos@senado.es</t>
@@ -18966,7 +19141,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -19001,6 +19176,11 @@
           <t>JMBarriosT</t>
         </is>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I445" t="inlineStr">
         <is>
           <t>jmaria.barrios@senado.es</t>
@@ -19060,6 +19240,11 @@
           <t>EBeltranHeredia</t>
         </is>
       </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Wed Jan 07</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>ebeltrandeheredia.bsky.social</t>
@@ -19092,6 +19277,11 @@
           <t>abeltran_ana</t>
         </is>
       </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I448" t="inlineStr">
         <is>
           <t>ana.beltran@senado.es</t>
@@ -19153,7 +19343,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -19190,7 +19380,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -19225,6 +19415,11 @@
           <t>LluisaBlanch</t>
         </is>
       </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Wed Apr 09</t>
+        </is>
+      </c>
       <c r="I452" t="inlineStr">
         <is>
           <t>lluisa.blanch@senado.es</t>
@@ -19259,7 +19454,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
@@ -19345,7 +19540,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
@@ -19377,7 +19572,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -19424,7 +19619,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -19461,7 +19656,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -19528,6 +19723,11 @@
           <t>emma_buj</t>
         </is>
       </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Wed Apr 29</t>
+        </is>
+      </c>
       <c r="I461" t="inlineStr">
         <is>
           <t>emma.buj@senado.es</t>
@@ -19560,6 +19760,11 @@
           <t>maria_caballero</t>
         </is>
       </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I462" t="inlineStr">
         <is>
           <t>maria.caballero@senado.es</t>
@@ -19678,6 +19883,11 @@
           <t>gerardo_camps</t>
         </is>
       </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I466" t="inlineStr">
         <is>
           <t>gerardo.camps@senado.es</t>
@@ -19710,6 +19920,11 @@
           <t>ConsolCantenys</t>
         </is>
       </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I467" t="inlineStr">
         <is>
           <t>consol.cantenys@senado.es</t>
@@ -19769,6 +19984,11 @@
           <t>JesusJCarnero</t>
         </is>
       </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I469" t="inlineStr">
         <is>
           <t>jjulio.carnero@senado.es</t>
@@ -19801,6 +20021,11 @@
           <t>jesuscaroada</t>
         </is>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Thu Apr 29</t>
+        </is>
+      </c>
       <c r="I470" t="inlineStr">
         <is>
           <t>jesus.caro@senado.es</t>
@@ -19862,7 +20087,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -19897,6 +20122,11 @@
           <t>CundoCaso</t>
         </is>
       </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Wed May 06</t>
+        </is>
+      </c>
       <c r="I473" t="inlineStr">
         <is>
           <t>secundino.caso@senado.es</t>
@@ -19929,6 +20159,11 @@
           <t>lauracastelfort</t>
         </is>
       </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>lauracastelfort.bsky.social</t>
@@ -19936,7 +20171,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -19973,7 +20208,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -20010,7 +20245,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -20045,6 +20280,11 @@
           <t>lucascrgu</t>
         </is>
       </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K477" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -20074,7 +20314,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -20109,6 +20349,11 @@
           <t>gcg55</t>
         </is>
       </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>gabicolome.bsky.social</t>
@@ -20153,7 +20398,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -20217,7 +20462,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -20247,6 +20492,11 @@
           <t>sevecuesta70</t>
         </is>
       </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I483" t="inlineStr">
         <is>
           <t>seve.cuesta@senado.es</t>
@@ -20306,6 +20556,11 @@
           <t>Esteladm_</t>
         </is>
       </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I485" t="inlineStr">
         <is>
           <t>ecarmen.darocas@senado.es</t>
@@ -20340,7 +20595,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -20382,7 +20637,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -20417,6 +20672,11 @@
           <t>cristinadiaztv</t>
         </is>
       </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I488" t="inlineStr">
         <is>
           <t>cristina.diaz@senado.es</t>
@@ -20449,6 +20709,11 @@
           <t>susanadiaz</t>
         </is>
       </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>susanadiaz.bsky.social</t>
@@ -20493,7 +20758,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -20528,6 +20793,11 @@
           <t>rociodivcon</t>
         </is>
       </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K491" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -20557,7 +20827,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -20567,7 +20837,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -20602,6 +20872,11 @@
           <t>_PepeEntrena</t>
         </is>
       </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I493" t="inlineStr">
         <is>
           <t>jose.entrena@senado.es</t>
@@ -20634,6 +20909,11 @@
           <t>_JuanEspadas</t>
         </is>
       </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>juanespadas.bsky.social</t>
@@ -20678,7 +20958,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -20745,6 +21025,11 @@
           <t>mdetxano</t>
         </is>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I497" t="inlineStr">
         <is>
           <t>mdolores.etxano@senado.es</t>
@@ -20858,6 +21143,11 @@
           <t>ifedezg</t>
         </is>
       </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K501" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -20887,7 +21177,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
@@ -20917,6 +21207,11 @@
           <t>MariaFdezAlv</t>
         </is>
       </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Sun May 10</t>
+        </is>
+      </c>
       <c r="I503" t="inlineStr">
         <is>
           <t>maria.fernandez@senado.es</t>
@@ -21116,7 +21411,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -21151,6 +21446,11 @@
           <t>JCarlosGarciaD</t>
         </is>
       </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Thu Mar 05</t>
+        </is>
+      </c>
       <c r="I510" t="inlineStr">
         <is>
           <t>jcarlos.garcia@senado.es</t>
@@ -21210,6 +21510,11 @@
           <t>miriamgarcianv1</t>
         </is>
       </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>miriamrgarcia.bsky.social</t>
@@ -21281,7 +21586,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -21316,6 +21621,11 @@
           <t>Jorvecom</t>
         </is>
       </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Wed May 06</t>
+        </is>
+      </c>
       <c r="I515" t="inlineStr">
         <is>
           <t>jorge.garcia@senado.es</t>
@@ -21375,6 +21685,11 @@
           <t>MJGarciaPelayo</t>
         </is>
       </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I517" t="inlineStr">
         <is>
           <t>mjose.garcia-pelayo@senado.es</t>
@@ -21407,6 +21722,11 @@
           <t>abigailgarrido</t>
         </is>
       </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Sun Oct 30</t>
+        </is>
+      </c>
       <c r="I518" t="inlineStr">
         <is>
           <t>abigail.garrido@senado.es</t>
@@ -21441,7 +21761,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -21476,6 +21796,11 @@
           <t>alfonsogil</t>
         </is>
       </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>alfonsogil.bsky.social</t>
@@ -21518,6 +21843,11 @@
           <t>RaquelGBenito</t>
         </is>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I521" t="inlineStr">
         <is>
           <t>raquel.gonzalez@senado.es</t>
@@ -21550,6 +21880,11 @@
           <t>Juan_MaGonzalez</t>
         </is>
       </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Wed May 06</t>
+        </is>
+      </c>
       <c r="K522" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -21577,6 +21912,11 @@
           <t>victorgf87</t>
         </is>
       </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Sat May 09</t>
+        </is>
+      </c>
       <c r="K523" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -21604,6 +21944,11 @@
           <t>pabloppgijon</t>
         </is>
       </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I524" t="inlineStr">
         <is>
           <t>pablogonzalez.senado@gmail.com</t>
@@ -21685,6 +22030,11 @@
           <t>MGrados98683</t>
         </is>
       </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Thu Mar 12</t>
+        </is>
+      </c>
       <c r="K527" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -21712,6 +22062,11 @@
           <t>RGranadosR</t>
         </is>
       </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="K528" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -21739,6 +22094,11 @@
           <t>agricola_lorew</t>
         </is>
       </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I529" t="inlineStr">
         <is>
           <t>lorena.guerra@senado.es</t>
@@ -21771,6 +22131,11 @@
           <t>otazu35</t>
         </is>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I530" t="inlineStr">
         <is>
           <t>fernando.gutierrez@senado.es</t>
@@ -21805,7 +22170,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -21842,7 +22207,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>Wed May 06</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -21906,7 +22271,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -21943,7 +22308,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -21980,7 +22345,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -21990,7 +22355,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -22025,6 +22390,11 @@
           <t>amarohuelva</t>
         </is>
       </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I537" t="inlineStr">
         <is>
           <t>amaro.huelva@senado.es</t>
@@ -22057,6 +22427,11 @@
           <t>YolandaIbarrola</t>
         </is>
       </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Mon Mar 23</t>
+        </is>
+      </c>
       <c r="K538" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -22162,7 +22537,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>Fri Jan 05</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
@@ -22194,7 +22569,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -22241,7 +22616,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -22286,6 +22661,11 @@
           <t>LemusCandidato</t>
         </is>
       </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Thu May 10</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
           <t>rafaellemus.bsky.social</t>
@@ -22330,7 +22710,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -22367,12 +22747,17 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed Apr 22</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>julialiberal.bsky.social</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -22407,6 +22792,11 @@
           <t>MARIAEUGENIAL</t>
         </is>
       </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Fri May 08</t>
+        </is>
+      </c>
       <c r="I548" t="inlineStr">
         <is>
           <t>meugenia.limon@senado.es</t>
@@ -22441,7 +22831,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -22513,6 +22903,11 @@
           <t>AntonioLuengoPP</t>
         </is>
       </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I551" t="inlineStr">
         <is>
           <t>antonioluengozapata@gmail.com</t>
@@ -22545,6 +22940,11 @@
           <t>mangelesluna2</t>
         </is>
       </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I552" t="inlineStr">
         <is>
           <t>mangeles.luna@senado.es</t>
@@ -22577,6 +22977,11 @@
           <t>a_lopezmoya</t>
         </is>
       </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I553" t="inlineStr">
         <is>
           <t>antonia.lopez@senado.es</t>
@@ -22631,6 +23036,11 @@
           <t>CarmenB2378</t>
         </is>
       </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Mon Mar 16</t>
+        </is>
+      </c>
       <c r="K555" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -22660,7 +23070,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -22702,7 +23112,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -22739,7 +23149,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -22774,6 +23184,11 @@
           <t>AmparoMarcoGual</t>
         </is>
       </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I559" t="inlineStr">
         <is>
           <t>mamparo.marco@senado.es</t>
@@ -22808,7 +23223,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>Sun Apr 26</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -22843,6 +23258,11 @@
           <t>JavierMaroto</t>
         </is>
       </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Sun May 10</t>
+        </is>
+      </c>
       <c r="K561" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -22872,7 +23292,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -22934,6 +23354,11 @@
           <t>PedroMartinTfe</t>
         </is>
       </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Mon Apr 21</t>
+        </is>
+      </c>
       <c r="K564" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -22961,6 +23386,11 @@
           <t>LirioMartin</t>
         </is>
       </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I565" t="inlineStr">
         <is>
           <t>mlirio.martin@senado.es</t>
@@ -22993,6 +23423,11 @@
           <t>JuntosSotillo</t>
         </is>
       </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Sat Apr 25</t>
+        </is>
+      </c>
       <c r="I566" t="inlineStr">
         <is>
           <t>jpablo.martin@senado.es</t>
@@ -23025,6 +23460,11 @@
           <t>paloma_martinm</t>
         </is>
       </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I567" t="inlineStr">
         <is>
           <t>paloma.martin@senado.es</t>
@@ -23059,7 +23499,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Sun Apr 26</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -23131,6 +23571,11 @@
           <t>AraMtnezEsteban</t>
         </is>
       </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I570" t="inlineStr">
         <is>
           <t>araceli.martinez@senado.es</t>
@@ -23163,6 +23608,11 @@
           <t>Antonio_Mtnz</t>
         </is>
       </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Sat May 09</t>
+        </is>
+      </c>
       <c r="I571" t="inlineStr">
         <is>
           <t>antonio.martinez@senado.es</t>
@@ -23224,7 +23674,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -23364,7 +23814,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -23399,6 +23849,11 @@
           <t>AlejoMdeLarra</t>
         </is>
       </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I579" t="inlineStr">
         <is>
           <t>alejo.miranda@senado.es</t>
@@ -23458,6 +23913,11 @@
           <t>Cesarmogoz</t>
         </is>
       </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I581" t="inlineStr">
         <is>
           <t>cesar.mogo@senado.es</t>
@@ -23546,7 +24006,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -23657,6 +24117,11 @@
           <t>EnricMorera_</t>
         </is>
       </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>enricmorera.bsky.social</t>
@@ -23664,7 +24129,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -23701,7 +24166,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -23746,6 +24211,11 @@
           <t>MurMelania</t>
         </is>
       </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I590" t="inlineStr">
         <is>
           <t>melania.mur@senado.es</t>
@@ -23780,7 +24250,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -23815,6 +24285,11 @@
           <t>javiermarquezsa</t>
         </is>
       </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I592" t="inlineStr">
         <is>
           <t>fjavier.marquez@senado.es</t>
@@ -23886,7 +24361,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>Mon May 11</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -23948,6 +24423,11 @@
           <t>txemaoleaga</t>
         </is>
       </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Wed Apr 29</t>
+        </is>
+      </c>
       <c r="I596" t="inlineStr">
         <is>
           <t>txema.oleaga@senado.es</t>
@@ -24007,6 +24487,11 @@
           <t>EvaOrtizVilella</t>
         </is>
       </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I598" t="inlineStr">
         <is>
           <t>eva.ortiz@senado.es</t>
@@ -24039,6 +24524,11 @@
           <t>ona_dionis</t>
         </is>
       </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Thu Sep 29</t>
+        </is>
+      </c>
       <c r="I599" t="inlineStr">
         <is>
           <t>dionis.ona@senado.es</t>
@@ -24098,6 +24588,11 @@
           <t>mtpallares</t>
         </is>
       </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K601" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -24125,6 +24620,11 @@
           <t>PepaPardo3</t>
         </is>
       </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I602" t="inlineStr">
         <is>
           <t>mjose.pardo@senado.es</t>
@@ -24159,7 +24659,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -24169,7 +24669,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -24231,6 +24731,11 @@
           <t>apolancoreb</t>
         </is>
       </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I605" t="inlineStr">
         <is>
           <t>calfonso.polanco@senado.es</t>
@@ -24265,7 +24770,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -24307,7 +24812,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -24344,7 +24849,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Wed Mar 18</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -24379,6 +24884,11 @@
           <t>fernandopriego</t>
         </is>
       </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Sun Jul 02</t>
+        </is>
+      </c>
       <c r="I609" t="inlineStr">
         <is>
           <t>fernando.priego@senado.es</t>
@@ -24411,6 +24921,11 @@
           <t>BenjamnPrieto</t>
         </is>
       </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Wed Nov 19</t>
+        </is>
+      </c>
       <c r="K610" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -24438,6 +24953,11 @@
           <t>PujolBonell</t>
         </is>
       </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I611" t="inlineStr">
         <is>
           <t>eduard.pujol@senado.es</t>
@@ -24470,6 +24990,11 @@
           <t>CarmenPrezBecer</t>
         </is>
       </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Mon May 11</t>
+        </is>
+      </c>
       <c r="I612" t="inlineStr">
         <is>
           <t>mcarmen.perez@senado.es</t>
@@ -24593,6 +25118,11 @@
           <t>eredondogamero</t>
         </is>
       </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="K616" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -24620,6 +25150,11 @@
           <t>JosManReyVarela</t>
         </is>
       </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Tue Sep 22</t>
+        </is>
+      </c>
       <c r="I617" t="inlineStr">
         <is>
           <t>jmanuel.rey@senado.es</t>
@@ -24654,7 +25189,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -24767,7 +25302,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -24814,7 +25349,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -24945,6 +25480,11 @@
           <t>cromeroher</t>
         </is>
       </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Thu Sep 28</t>
+        </is>
+      </c>
       <c r="I627" t="inlineStr">
         <is>
           <t>carmelo.romero@senado.es</t>
@@ -24979,7 +25519,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -25024,6 +25564,11 @@
           <t>madelarosapp</t>
         </is>
       </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="E629" t="inlineStr">
         <is>
           <t>migueldelarl.bsky.social</t>
@@ -25066,6 +25611,11 @@
           <t>nurovira75</t>
         </is>
       </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Mon Feb 10</t>
+        </is>
+      </c>
       <c r="K630" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -25147,6 +25697,11 @@
           <t>eruizescudero</t>
         </is>
       </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>rrenrique.bsky.social</t>
@@ -25213,7 +25768,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -25250,7 +25805,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -25297,7 +25852,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -25332,6 +25887,11 @@
           <t>MariaSalomColl</t>
         </is>
       </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Wed Apr 29</t>
+        </is>
+      </c>
       <c r="I638" t="inlineStr">
         <is>
           <t>maria.salom@senado.es</t>
@@ -25440,6 +26000,11 @@
           <t>LuisStamaria</t>
         </is>
       </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Tue May 12</t>
+        </is>
+      </c>
       <c r="I642" t="inlineStr">
         <is>
           <t>ljavier.santamaria@senado.es</t>
@@ -25474,7 +26039,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -25506,7 +26071,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>2020-02-11</t>
+          <t>Tue Feb 11</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -25541,6 +26106,11 @@
           <t>SerranoArenales</t>
         </is>
       </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Sun Dec 20</t>
+        </is>
+      </c>
       <c r="K645" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -25597,7 +26167,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -25681,6 +26251,11 @@
           <t>carmelasilva</t>
         </is>
       </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="K650" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -25710,7 +26285,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
@@ -25740,6 +26315,11 @@
           <t>Msolersantos</t>
         </is>
       </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Wed Apr 29</t>
+        </is>
+      </c>
       <c r="K652" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -25769,7 +26349,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -25809,6 +26389,11 @@
           <t>eloysuarezl</t>
         </is>
       </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Wed May 13</t>
+        </is>
+      </c>
       <c r="I654" t="inlineStr">
         <is>
           <t>eloy.suarez@senado.es</t>
@@ -25841,6 +26426,11 @@
           <t>piedadsanchezg</t>
         </is>
       </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I655" t="inlineStr">
         <is>
           <t>piedad.sanchez@senado.es</t>
@@ -25875,7 +26465,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -25910,6 +26500,11 @@
           <t>Inma_Roca</t>
         </is>
       </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I657" t="inlineStr">
         <is>
           <t>inmaculada.sanchez@senado.es</t>
@@ -25942,6 +26537,11 @@
           <t>KilianSanjuan</t>
         </is>
       </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I658" t="inlineStr">
         <is>
           <t>kilian.sanchez@senado.es</t>
@@ -25976,7 +26576,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26013,7 +26613,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -26099,7 +26699,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -26171,6 +26771,11 @@
           <t>luistudanca</t>
         </is>
       </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E665" t="inlineStr">
         <is>
           <t>luistudanca.bsky.social</t>
@@ -26264,7 +26869,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -26311,7 +26916,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -26348,7 +26953,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -26385,7 +26990,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -26449,7 +27054,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -26484,6 +27089,11 @@
           <t>MariaJosVillal4</t>
         </is>
       </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I674" t="inlineStr">
         <is>
           <t>mjose.villalba@senado.es</t>
@@ -26516,6 +27126,11 @@
           <t>LuciaYeves</t>
         </is>
       </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Sun May 10</t>
+        </is>
+      </c>
       <c r="I675" t="inlineStr">
         <is>
           <t>lucia.yeves@senado.es</t>
@@ -26550,7 +27165,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>Sun May 10</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -26585,6 +27200,11 @@
           <t>PilarZamoracr</t>
         </is>
       </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Wed Apr 22</t>
+        </is>
+      </c>
       <c r="K677" t="inlineStr">
         <is>
           <t>Senador/a</t>
@@ -26614,7 +27234,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -26678,7 +27298,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -26715,7 +27335,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -26752,7 +27372,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -26762,7 +27382,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -26789,7 +27409,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -26816,7 +27436,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>Tue Jan 21</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -26826,7 +27446,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -26853,7 +27473,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -26863,7 +27483,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -26890,7 +27510,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -26927,7 +27547,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -26937,7 +27557,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -26964,7 +27584,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -26996,7 +27616,7 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -27023,7 +27643,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -27055,7 +27675,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -27065,7 +27685,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -27092,7 +27712,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -27102,7 +27722,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -27139,7 +27759,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -27176,7 +27796,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -27186,7 +27806,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -27213,7 +27833,7 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>2015-02-04</t>
+          <t>Wed Feb 04</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -27223,7 +27843,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -27250,7 +27870,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -27260,7 +27880,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -27287,7 +27907,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>Thu Mar 05</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -27324,7 +27944,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -27351,7 +27971,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -27378,7 +27998,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -27405,7 +28025,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -27432,7 +28052,7 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -27469,7 +28089,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -27496,7 +28116,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -27533,7 +28153,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -27560,7 +28180,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -27587,7 +28207,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -27624,7 +28244,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>Fri Mar 27</t>
         </is>
       </c>
     </row>
@@ -27649,6 +28269,11 @@
           <t>seacabolafiesta</t>
         </is>
       </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2024-11-23</t>
+        </is>
+      </c>
       <c r="I709" t="inlineStr">
         <is>
           <t>info@seacabolafiesta.com</t>
@@ -27673,7 +28298,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Fri May 08</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -27710,7 +28335,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -27752,7 +28377,7 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -27794,7 +28419,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -27836,7 +28461,7 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -27871,6 +28496,11 @@
           <t>Jorge_Azcon</t>
         </is>
       </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="I715" t="inlineStr">
         <is>
           <t>gabinetepresidente@aragon.es</t>
@@ -27910,7 +28540,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -27952,7 +28582,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -28031,7 +28661,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -28068,7 +28698,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -28110,7 +28740,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -28152,7 +28782,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -28189,7 +28819,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -28231,7 +28861,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -28273,7 +28903,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -28315,7 +28945,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -28325,7 +28955,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -28362,7 +28992,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -28404,7 +29034,7 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -28441,7 +29071,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -28478,7 +29108,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -28557,7 +29187,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>Fri Dec 12</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -28594,7 +29224,7 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -28636,7 +29266,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -28752,7 +29382,7 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -28789,7 +29419,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -28831,7 +29461,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -28873,7 +29503,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Thu May 07</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -28910,7 +29540,7 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -28999,7 +29629,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>Thu Feb 12</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -29036,7 +29666,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -29073,7 +29703,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -29115,7 +29745,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -29152,7 +29782,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -29189,7 +29819,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -29231,7 +29861,7 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -29268,7 +29898,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -29305,7 +29935,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -29362,7 +29992,7 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -29399,7 +30029,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -29441,7 +30071,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>Sun Dec 08</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -29515,7 +30145,7 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -29557,7 +30187,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Tue May 12</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -29599,7 +30229,7 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -29636,7 +30266,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -29673,7 +30303,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -29683,7 +30313,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -29725,7 +30355,7 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -29762,7 +30392,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -29809,7 +30439,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -29893,7 +30523,7 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -29940,7 +30570,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -29982,7 +30612,7 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -29992,7 +30622,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -30024,7 +30654,7 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
@@ -30071,7 +30701,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -30103,7 +30733,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -30135,7 +30765,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>Mon May 04</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -30167,7 +30797,7 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -30204,7 +30834,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
@@ -30244,6 +30874,11 @@
           <t>pablodeolavide</t>
         </is>
       </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Thu Jan 30</t>
+        </is>
+      </c>
       <c r="E774" t="inlineStr">
         <is>
           <t>pablodeolavide.upo.es</t>
@@ -30251,7 +30886,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -30283,7 +30918,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -30315,7 +30950,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
@@ -30325,7 +30960,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -30357,7 +30992,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -30394,7 +31029,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -30404,7 +31039,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -30436,7 +31071,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -30478,7 +31113,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>Tue Feb 17</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -30488,7 +31123,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -30557,7 +31192,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
@@ -30567,7 +31202,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -30599,7 +31234,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -30631,7 +31266,7 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
@@ -30641,7 +31276,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -30673,7 +31308,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -30710,7 +31345,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>Mon Jan 20</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
@@ -30720,7 +31355,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -30752,7 +31387,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -30784,7 +31419,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -30794,7 +31429,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -30826,7 +31461,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Wed May 13</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
@@ -30868,7 +31503,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
@@ -30878,7 +31513,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -30910,7 +31545,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -30947,7 +31582,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -30989,7 +31624,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -31021,7 +31656,7 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -31053,7 +31688,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -31063,7 +31698,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -31095,7 +31730,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -31105,7 +31740,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -31137,7 +31772,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>2011-11-15</t>
+          <t>Tue Nov 15</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
@@ -31147,7 +31782,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -31179,7 +31814,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -31216,7 +31851,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>Fri Jan 24</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -31226,7 +31861,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -31256,6 +31891,11 @@
           <t>uva_es</t>
         </is>
       </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
+        </is>
+      </c>
       <c r="E800" t="inlineStr">
         <is>
           <t>uva-es.bsky.social</t>
@@ -31263,7 +31903,7 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -31295,7 +31935,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>Tue May 05</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -31305,7 +31945,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -31337,7 +31977,7 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>Tue Mar 18</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
@@ -31347,7 +31987,7 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -31379,7 +32019,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>Fri Jan 31</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -31389,7 +32029,7 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -31421,7 +32061,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>Thu Dec 05</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -31431,7 +32071,7 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -31463,7 +32103,7 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
@@ -31473,7 +32113,7 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -31505,7 +32145,7 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>Mon Feb 24</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
@@ -31515,7 +32155,7 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -31547,7 +32187,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>Fri Jan 17</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -31557,7 +32197,7 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -31589,7 +32229,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>Wed Apr 30</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -31631,7 +32271,7 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -31668,7 +32308,7 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>Wed Feb 11</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -31678,7 +32318,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -31710,7 +32350,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -31720,7 +32360,7 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -31752,7 +32392,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>Fri Nov 15</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -31762,7 +32402,7 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -31794,7 +32434,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>Wed Jul 30</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -31804,7 +32444,7 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -31836,7 +32476,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -31846,7 +32486,7 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -31878,7 +32518,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -31888,7 +32528,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -31920,7 +32560,7 @@
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>Fri Nov 29</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -31930,7 +32570,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -31980,6 +32620,11 @@
       <c r="C818" t="inlineStr">
         <is>
           <t>sbrez1981</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Thu May 14</t>
         </is>
       </c>
       <c r="K818" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -27725,16 +27725,6 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="G692" t="inlineStr">
-        <is>
-          <t>izquierda_unida</t>
-        </is>
-      </c>
-      <c r="H692" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
       <c r="I692" t="inlineStr">
         <is>
           <t>comunicacion@izquierda-unida.es</t>
@@ -29946,11 +29936,6 @@
       <c r="F751" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="G751" t="inlineStr">
-        <is>
-          <t>izquierda_unida</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -15946,6 +15946,16 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>enriquesantiago@mastodon.social</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="I365" t="inlineStr">
         <is>
           <t>enrique.santiago@congreso.es</t>
@@ -16344,6 +16354,16 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>franciscosierra@mastodon.social</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="I374" t="inlineStr">
         <is>
           <t>francisco.sierra@congreso.es</t>
@@ -27721,6 +27741,16 @@
         </is>
       </c>
       <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>izquierda_unida@mastodon.social</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -3860,6 +3860,16 @@
           <t>Thu May 14</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>teshsidi.bsky.social</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>teshsidi@congreso.es</t>

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -20630,12 +20630,12 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>carladelgado.bsky.social</t>
+          <t>carlaantonelli.bsky.social</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -1946,7 +1946,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>lyadelestado</t>
+          <t>lyadelestado.bsky.social</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14171,16 +14171,6 @@
           <t>Thu May 14</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>joseframirez.bsky.social</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
       <c r="I325" t="inlineStr">
         <is>
           <t>jose.ramirez@congreso.es</t>
@@ -14935,16 +14925,6 @@
           <t>Thu May 14</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>santirodriguez.bsky.social</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
       <c r="I342" t="inlineStr">
         <is>
           <t>santi.rodriguez@congreso.es</t>
@@ -23559,16 +23539,6 @@
           <t>Martínez Antolín, Jorge Domingo</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>jorgemtnez.bsky.social</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
       <c r="I569" t="inlineStr">
         <is>
           <t>jdomingo.martinez@senado.es</t>
@@ -28296,7 +28266,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>seacabolafiesta</t>
+          <t>seacabolafiesta.bsky.social</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -15421,7 +15421,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>gabrielrufian.bsky.social</t>
+          <t>grufian.bsky.social</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -7911,6 +7911,11 @@
           <t>centromemorialvt.bsky.social</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
       <c r="J230" t="inlineStr">
         <is>
           <t>Fundación Estatal</t>
@@ -8796,7 +8801,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -9128,7 +9133,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -9214,7 +9219,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -9246,7 +9251,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -9386,7 +9391,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -9546,7 +9551,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -9804,7 +9809,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -9954,7 +9959,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -9986,7 +9991,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -10028,7 +10033,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -10070,7 +10075,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -10198,7 +10203,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -10388,7 +10393,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -10430,7 +10435,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -10472,7 +10477,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -10514,7 +10519,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -10620,7 +10625,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -10694,7 +10699,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -10763,7 +10768,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -11173,7 +11178,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -11450,7 +11455,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -11942,7 +11947,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -12335,7 +12340,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -12681,7 +12686,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -13689,7 +13694,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -14685,7 +14690,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -15787,7 +15792,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -15955,7 +15960,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -16091,7 +16096,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -16803,7 +16808,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -17092,7 +17097,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -17836,7 +17841,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -18308,7 +18313,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -18402,7 +18407,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -18449,7 +18454,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -18815,7 +18820,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -20312,7 +20317,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -23453,7 +23458,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -23547,7 +23552,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -23557,7 +23562,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -23955,7 +23960,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -24153,7 +24158,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -24605,7 +24610,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -25544,7 +25549,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -28219,7 +28224,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
@@ -28451,7 +28456,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -28582,7 +28587,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -31703,7 +31708,7 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -34906,7 +34911,7 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -34970,7 +34975,7 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -35007,7 +35012,7 @@
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
@@ -35081,7 +35086,7 @@
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -35209,7 +35214,7 @@
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -35246,7 +35251,7 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
@@ -35256,7 +35261,7 @@
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -35367,7 +35372,7 @@
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
@@ -35404,7 +35409,7 @@
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
@@ -36449,7 +36454,7 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -37747,7 +37752,7 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -40191,7 +40196,7 @@
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K1084" t="inlineStr">
@@ -41307,7 +41312,7 @@
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K1117" t="inlineStr">
@@ -41864,7 +41869,7 @@
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K1133" t="inlineStr">
@@ -43354,7 +43359,7 @@
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K1178" t="inlineStr">
@@ -46447,7 +46452,7 @@
       </c>
       <c r="F1267" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K1267" t="inlineStr">
@@ -48729,7 +48734,7 @@
       </c>
       <c r="F1333" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I1333" t="inlineStr">
@@ -48771,7 +48776,7 @@
       </c>
       <c r="F1334" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1334" t="inlineStr">
@@ -48813,7 +48818,7 @@
       </c>
       <c r="F1335" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1335" t="inlineStr">
@@ -48961,7 +48966,7 @@
       </c>
       <c r="F1339" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1339" t="inlineStr">
@@ -49008,7 +49013,7 @@
       </c>
       <c r="F1340" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1340" t="inlineStr">
@@ -49082,7 +49087,7 @@
       </c>
       <c r="F1342" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1342" t="inlineStr">
@@ -49161,7 +49166,7 @@
       </c>
       <c r="F1344" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1344" t="inlineStr">
@@ -49245,7 +49250,7 @@
       </c>
       <c r="F1346" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1346" t="inlineStr">
@@ -49324,7 +49329,7 @@
       </c>
       <c r="F1348" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1348" t="inlineStr">
@@ -49403,7 +49408,7 @@
       </c>
       <c r="F1350" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1350" t="inlineStr">
@@ -49482,7 +49487,7 @@
       </c>
       <c r="F1352" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1352" t="inlineStr">
@@ -49556,7 +49561,7 @@
       </c>
       <c r="F1354" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1354" t="inlineStr">
@@ -49640,7 +49645,7 @@
       </c>
       <c r="F1356" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1356" t="inlineStr">
@@ -49751,7 +49756,7 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I1359" t="inlineStr">
@@ -49825,7 +49830,7 @@
       </c>
       <c r="F1361" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1361" t="inlineStr">
@@ -49867,7 +49872,7 @@
       </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1362" t="inlineStr">
@@ -49909,7 +49914,7 @@
       </c>
       <c r="F1363" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1363" t="inlineStr">
@@ -49951,7 +49956,7 @@
       </c>
       <c r="F1364" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1364" t="inlineStr">
@@ -49993,7 +49998,7 @@
       </c>
       <c r="F1365" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1365" t="inlineStr">
@@ -50035,7 +50040,7 @@
       </c>
       <c r="F1366" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I1366" t="inlineStr">
@@ -50077,7 +50082,7 @@
       </c>
       <c r="F1367" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I1367" t="inlineStr">
@@ -50119,7 +50124,7 @@
       </c>
       <c r="F1368" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I1368" t="inlineStr">
@@ -50161,7 +50166,7 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1369" t="inlineStr">
@@ -50203,7 +50208,7 @@
       </c>
       <c r="F1370" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1370" t="inlineStr">
@@ -50245,7 +50250,7 @@
       </c>
       <c r="F1371" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1371" t="inlineStr">
@@ -50287,7 +50292,7 @@
       </c>
       <c r="F1372" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1372" t="inlineStr">
@@ -50329,7 +50334,7 @@
       </c>
       <c r="F1373" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1373" t="inlineStr">
@@ -50455,7 +50460,7 @@
       </c>
       <c r="F1376" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1376" t="inlineStr">
@@ -50497,7 +50502,7 @@
       </c>
       <c r="F1377" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1377" t="inlineStr">
@@ -50539,7 +50544,7 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1378" t="inlineStr">
@@ -50581,7 +50586,7 @@
       </c>
       <c r="F1379" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I1379" t="inlineStr">
@@ -50623,7 +50628,7 @@
       </c>
       <c r="F1380" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1380" t="inlineStr">
@@ -50665,7 +50670,7 @@
       </c>
       <c r="F1381" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1381" t="inlineStr">
@@ -50707,7 +50712,7 @@
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I1382" t="inlineStr">
@@ -50982,7 +50987,7 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J1392" t="inlineStr">
@@ -51019,7 +51024,7 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J1393" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
@@ -17569,7 +17569,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -19346,7 +19346,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -19736,7 +19736,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -21335,7 +21335,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -21933,7 +21933,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -22988,7 +22988,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -23228,7 +23228,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -23856,7 +23856,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -23898,7 +23898,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -24479,7 +24479,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -24558,7 +24558,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -24778,7 +24778,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -24862,7 +24862,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -25129,7 +25129,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -25371,7 +25371,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -25769,7 +25769,7 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
@@ -26065,7 +26065,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -26161,7 +26161,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -26198,7 +26198,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -26319,7 +26319,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -26558,7 +26558,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -26659,7 +26659,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -27083,7 +27083,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -27541,7 +27541,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -27706,7 +27706,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -28081,7 +28081,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
@@ -28256,7 +28256,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
@@ -28828,7 +28828,7 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -28961,7 +28961,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -29067,7 +29067,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -29131,7 +29131,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -29232,7 +29232,7 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -29296,7 +29296,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -29407,7 +29407,7 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
@@ -29454,7 +29454,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -29641,7 +29641,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
@@ -29673,7 +29673,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
@@ -29705,7 +29705,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -29742,7 +29742,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -29917,7 +29917,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -30225,7 +30225,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -30299,7 +30299,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -30336,7 +30336,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -30383,7 +30383,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -30420,7 +30420,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -30494,7 +30494,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -30659,7 +30659,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -30701,7 +30701,7 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -30775,7 +30775,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -30812,7 +30812,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -30977,7 +30977,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -31014,7 +31014,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -31088,7 +31088,7 @@
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -31189,7 +31189,7 @@
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -31393,7 +31393,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -31698,7 +31698,7 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -31745,7 +31745,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -31792,7 +31792,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -32068,7 +32068,7 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -32169,7 +32169,7 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K853" t="inlineStr">
@@ -32201,7 +32201,7 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -32302,7 +32302,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -32689,7 +32689,7 @@
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K868" t="inlineStr">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -32871,7 +32871,7 @@
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -33088,7 +33088,7 @@
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -33248,7 +33248,7 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="K885" t="inlineStr">
@@ -33307,7 +33307,7 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -33344,7 +33344,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -33391,7 +33391,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -33541,7 +33541,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -33578,7 +33578,7 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K895" t="inlineStr">
@@ -33706,7 +33706,7 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="K902" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K903" t="inlineStr">
@@ -33856,7 +33856,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="K904" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -33967,7 +33967,7 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -34004,7 +34004,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -34238,7 +34238,7 @@
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -34398,7 +34398,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -34445,7 +34445,7 @@
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -34519,7 +34519,7 @@
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -34763,7 +34763,7 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -34827,7 +34827,7 @@
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -34901,7 +34901,7 @@
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -34911,7 +34911,7 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
@@ -34975,7 +34975,7 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -35002,7 +35002,7 @@
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -35113,7 +35113,7 @@
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
@@ -35172,7 +35172,7 @@
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -35204,7 +35204,7 @@
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -35251,7 +35251,7 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
@@ -35261,7 +35261,7 @@
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -35372,7 +35372,7 @@
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -40196,7 +40196,7 @@
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K1084" t="inlineStr">
@@ -48966,7 +48966,7 @@
       </c>
       <c r="F1339" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1339" t="inlineStr">
@@ -49166,7 +49166,7 @@
       </c>
       <c r="F1344" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1344" t="inlineStr">
@@ -49329,7 +49329,7 @@
       </c>
       <c r="F1348" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1348" t="inlineStr">
@@ -49487,7 +49487,7 @@
       </c>
       <c r="F1352" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I1352" t="inlineStr">
@@ -49561,7 +49561,7 @@
       </c>
       <c r="F1354" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1354" t="inlineStr">
@@ -49872,7 +49872,7 @@
       </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1362" t="inlineStr">
@@ -49914,7 +49914,7 @@
       </c>
       <c r="F1363" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1363" t="inlineStr">
@@ -49998,7 +49998,7 @@
       </c>
       <c r="F1365" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1365" t="inlineStr">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1369" t="inlineStr">
@@ -50250,7 +50250,7 @@
       </c>
       <c r="F1371" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="I1371" t="inlineStr">
@@ -50334,7 +50334,7 @@
       </c>
       <c r="F1373" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1373" t="inlineStr">
@@ -50502,7 +50502,7 @@
       </c>
       <c r="F1377" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1377" t="inlineStr">
@@ -50544,7 +50544,7 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1378" t="inlineStr">
@@ -50670,7 +50670,7 @@
       </c>
       <c r="F1381" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I1381" t="inlineStr">
@@ -50987,7 +50987,7 @@
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J1392" t="inlineStr">
@@ -51024,7 +51024,7 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J1393" t="inlineStr">

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1396"/>
+  <dimension ref="A1:R1396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,16 @@
           <t>Invente</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Twitter Última consulta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Twitter Estado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3309,24 +3319,24 @@
           <t>DeleGobCataluna</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>delegobcataluna.bsky.social</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Delegación del Gobierno</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>delegobcataluna.bsky.social</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Delegación del Gobierno</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
         </is>
       </c>
     </row>
@@ -5382,19 +5392,19 @@
           <t>Isdefe_</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Sociedad Mercantil Estatal</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>INV00003446</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Sociedad Mercantil Estatal</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>INV00003446</t>
         </is>
       </c>
     </row>
@@ -7574,19 +7584,19 @@
           <t>SevillaZF</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Entidad de Derecho Público</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>INV00001469</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>Entidad de Derecho Público</t>
-        </is>
-      </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>INV00001469</t>
         </is>
       </c>
     </row>
@@ -7739,19 +7749,19 @@
           <t>ENSAonline</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Sociedad Mercantil Estatal</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>INV00002097</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>Sociedad Mercantil Estatal</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>INV00002097</t>
         </is>
       </c>
     </row>
@@ -8917,19 +8927,19 @@
           <t>INSS_oficial</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Entidad Gestora de la S.S.</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>INV00003732</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>Entidad Gestora de la S.S.</t>
-        </is>
-      </c>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>INV00003732</t>
         </is>
       </c>
     </row>
@@ -11003,29 +11013,29 @@
           <t>jagirretxea</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>agirretxea@congreso.es</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Diputado/a</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Grupo Parlamentario Vasco (EAJ-PNV)</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Gipuzkoa</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>agirretxea@congreso.es</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Diputado/a</t>
-        </is>
-      </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>Grupo Parlamentario Vasco (EAJ-PNV)</t>
-        </is>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Gipuzkoa</t>
         </is>
       </c>
     </row>
@@ -11443,39 +11453,39 @@
           <t>AlonsoCantorne</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>alonsocantorne.bsky.social</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>alonso.cantorne@congreso.es</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Diputado/a</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Grupo Parlamentario Plurinacional SUMAR</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>alonsocantorne.bsky.social</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>alonso.cantorne@congreso.es</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Diputado/a</t>
-        </is>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>Grupo Parlamentario Plurinacional SUMAR</t>
-        </is>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>Tarragona</t>
         </is>
       </c>
     </row>
@@ -21565,29 +21575,29 @@
           <t>OscarRamajoPra</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>oscar.ramajo@congreso.es</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Diputado/a</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>Grupo Parlamentario Popular en el Congreso</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Zamora</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>oscar.ramajo@congreso.es</t>
-        </is>
-      </c>
-      <c r="K572" t="inlineStr">
-        <is>
-          <t>Diputado/a</t>
-        </is>
-      </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>Grupo Parlamentario Popular en el Congreso</t>
-        </is>
-      </c>
-      <c r="M572" t="inlineStr">
-        <is>
-          <t>Zamora</t>
         </is>
       </c>
     </row>
@@ -24353,27 +24363,32 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>carlos.sanchezojeda@congreso.es</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Diputado/a</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Grupo Parlamentario Popular en el Congreso</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Palmas (Las)</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="I635" t="inlineStr">
-        <is>
-          <t>carlos.sanchezojeda@congreso.es</t>
-        </is>
-      </c>
-      <c r="K635" t="inlineStr">
-        <is>
-          <t>Diputado/a</t>
-        </is>
-      </c>
-      <c r="L635" t="inlineStr">
-        <is>
-          <t>Grupo Parlamentario Popular en el Congreso</t>
-        </is>
-      </c>
-      <c r="M635" t="inlineStr">
-        <is>
-          <t>Palmas (Las)</t>
         </is>
       </c>
     </row>
@@ -28895,24 +28910,24 @@
           <t>marilo_flores91</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr">
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>mdolores.flores@senado.es</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Senador/a</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="I757" t="inlineStr">
-        <is>
-          <t>mdolores.flores@senado.es</t>
-        </is>
-      </c>
-      <c r="K757" t="inlineStr">
-        <is>
-          <t>Senador/a</t>
-        </is>
-      </c>
-      <c r="L757" t="inlineStr">
-        <is>
-          <t>GPS</t>
         </is>
       </c>
     </row>
@@ -32953,24 +32968,24 @@
           <t>PRojoNoguera</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>pilar.rojo@senado.es</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Senador/a</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>GPP</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="I876" t="inlineStr">
-        <is>
-          <t>pilar.rojo@senado.es</t>
-        </is>
-      </c>
-      <c r="K876" t="inlineStr">
-        <is>
-          <t>Senador/a</t>
-        </is>
-      </c>
-      <c r="L876" t="inlineStr">
-        <is>
-          <t>GPP</t>
         </is>
       </c>
     </row>
@@ -38086,24 +38101,24 @@
           <t>ArkauteAkademia</t>
         </is>
       </c>
-      <c r="D1020" t="inlineStr">
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Organismo Autónomo</t>
+        </is>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>País Vasco</t>
+        </is>
+      </c>
+      <c r="P1020" t="inlineStr">
+        <is>
+          <t>INV00000015</t>
+        </is>
+      </c>
+      <c r="R1020" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1020" t="inlineStr">
-        <is>
-          <t>Organismo Autónomo</t>
-        </is>
-      </c>
-      <c r="N1020" t="inlineStr">
-        <is>
-          <t>País Vasco</t>
-        </is>
-      </c>
-      <c r="P1020" t="inlineStr">
-        <is>
-          <t>INV00000015</t>
         </is>
       </c>
     </row>
@@ -38234,24 +38249,24 @@
           <t>aaconocimiento</t>
         </is>
       </c>
-      <c r="D1024" t="inlineStr">
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Agencia</t>
+        </is>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="P1024" t="inlineStr">
+        <is>
+          <t>INV00000048</t>
+        </is>
+      </c>
+      <c r="R1024" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1024" t="inlineStr">
-        <is>
-          <t>Agencia</t>
-        </is>
-      </c>
-      <c r="N1024" t="inlineStr">
-        <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
-      <c r="P1024" t="inlineStr">
-        <is>
-          <t>INV00000048</t>
         </is>
       </c>
     </row>
@@ -39807,24 +39822,24 @@
           <t>GVAavi</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr">
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>Ente Público</t>
+        </is>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="P1073" t="inlineStr">
+        <is>
+          <t>INV00000153</t>
+        </is>
+      </c>
+      <c r="R1073" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1073" t="inlineStr">
-        <is>
-          <t>Ente Público</t>
-        </is>
-      </c>
-      <c r="N1073" t="inlineStr">
-        <is>
-          <t>Comunitat Valenciana</t>
-        </is>
-      </c>
-      <c r="P1073" t="inlineStr">
-        <is>
-          <t>INV00000153</t>
         </is>
       </c>
     </row>
@@ -39982,24 +39997,24 @@
           <t>avpd_dbeb</t>
         </is>
       </c>
-      <c r="D1078" t="inlineStr">
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>Ente Público</t>
+        </is>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>País Vasco</t>
+        </is>
+      </c>
+      <c r="P1078" t="inlineStr">
+        <is>
+          <t>INV00000160</t>
+        </is>
+      </c>
+      <c r="R1078" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1078" t="inlineStr">
-        <is>
-          <t>Ente Público</t>
-        </is>
-      </c>
-      <c r="N1078" t="inlineStr">
-        <is>
-          <t>País Vasco</t>
-        </is>
-      </c>
-      <c r="P1078" t="inlineStr">
-        <is>
-          <t>INV00000160</t>
         </is>
       </c>
     </row>
@@ -40019,24 +40034,24 @@
           <t>AugasdeGalicia</t>
         </is>
       </c>
-      <c r="D1079" t="inlineStr">
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Entidad Pública Empresarial</t>
+        </is>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="P1079" t="inlineStr">
+        <is>
+          <t>INV00000186</t>
+        </is>
+      </c>
+      <c r="R1079" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1079" t="inlineStr">
-        <is>
-          <t>Entidad Pública Empresarial</t>
-        </is>
-      </c>
-      <c r="N1079" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="P1079" t="inlineStr">
-        <is>
-          <t>INV00000186</t>
         </is>
       </c>
     </row>
@@ -41384,24 +41399,24 @@
           <t>CNJCat</t>
         </is>
       </c>
-      <c r="D1119" t="inlineStr">
+      <c r="K1119" t="inlineStr">
+        <is>
+          <t>Ente Público</t>
+        </is>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>Catalunya</t>
+        </is>
+      </c>
+      <c r="P1119" t="inlineStr">
+        <is>
+          <t>INV00001313</t>
+        </is>
+      </c>
+      <c r="R1119" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1119" t="inlineStr">
-        <is>
-          <t>Ente Público</t>
-        </is>
-      </c>
-      <c r="N1119" t="inlineStr">
-        <is>
-          <t>Catalunya</t>
-        </is>
-      </c>
-      <c r="P1119" t="inlineStr">
-        <is>
-          <t>INV00001313</t>
         </is>
       </c>
     </row>
@@ -41968,24 +41983,24 @@
           <t>EVha_gva</t>
         </is>
       </c>
-      <c r="D1136" t="inlineStr">
+      <c r="K1136" t="inlineStr">
+        <is>
+          <t>Entidad Pública Empresarial</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="P1136" t="inlineStr">
+        <is>
+          <t>INV00002080</t>
+        </is>
+      </c>
+      <c r="R1136" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1136" t="inlineStr">
-        <is>
-          <t>Entidad Pública Empresarial</t>
-        </is>
-      </c>
-      <c r="N1136" t="inlineStr">
-        <is>
-          <t>Comunitat Valenciana</t>
-        </is>
-      </c>
-      <c r="P1136" t="inlineStr">
-        <is>
-          <t>INV00002080</t>
         </is>
       </c>
     </row>
@@ -47769,24 +47784,24 @@
           <t>saludextremadur</t>
         </is>
       </c>
-      <c r="D1304" t="inlineStr">
+      <c r="K1304" t="inlineStr">
+        <is>
+          <t>Organismo Autónomo</t>
+        </is>
+      </c>
+      <c r="N1304" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="P1304" t="inlineStr">
+        <is>
+          <t>INV00005050</t>
+        </is>
+      </c>
+      <c r="R1304" t="inlineStr">
         <is>
           <t>404</t>
-        </is>
-      </c>
-      <c r="K1304" t="inlineStr">
-        <is>
-          <t>Organismo Autónomo</t>
-        </is>
-      </c>
-      <c r="N1304" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="P1304" t="inlineStr">
-        <is>
-          <t>INV00005050</t>
         </is>
       </c>
     </row>

--- a/dataset/datosfinales.xlsx
+++ b/dataset/datosfinales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1396"/>
+  <dimension ref="A1:V1396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,26 @@
           <t>Twitter Estado</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Bluesky Última consulta</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Bluesky Estado</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Mastodon Última consulta</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Mastodon Estado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
